--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488197_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488197_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.931</v>
+        <v>8.039300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4788</v>
+        <v>7.7841</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4522</v>
+        <v>0.2552</v>
       </c>
       <c r="G2" t="n">
         <v>4.3957</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2582</v>
+        <v>-0.1499</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9637</v>
+        <v>-0.6584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7056</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.7199</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0895</v>
+        <v>6.6096</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4598</v>
+        <v>6.2754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6297</v>
+        <v>0.3342</v>
       </c>
       <c r="G3" t="n">
         <v>4.7662</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.472</v>
+        <v>-0.0078</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5633</v>
+        <v>-0.7477</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0353</v>
+        <v>0.7399</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0016</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7761</v>
+        <v>1.5375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.498</v>
+        <v>1.3479</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2782</v>
+        <v>0.1895</v>
       </c>
       <c r="G4" t="n">
-        <v>1.326</v>
+        <v>1.4596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4747</v>
+        <v>0.6315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6957</v>
+        <v>1.9402</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0215</v>
+        <v>1.1937</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6742</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6303</v>
+        <v>-0.4805</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8299</v>
+        <v>-0.3656</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1996</v>
+        <v>-0.115</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4501</v>
+        <v>-0.2192</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1977</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6479</v>
+        <v>0.373</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.01</v>
+        <v>1.5299</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1406</v>
+        <v>0.498</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1306</v>
+        <v>1.032</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4596</v>
+        <v>1.326</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6315</v>
+        <v>0.4747</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9402</v>
+        <v>0.6957</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1937</v>
+        <v>0.0215</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6742</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4805</v>
+        <v>0.6303</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3656</v>
+        <v>0.8299</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.115</v>
+        <v>-0.1996</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7466</v>
+        <v>0.2039</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7996</v>
+        <v>-0.1977</v>
       </c>
       <c r="U5" t="n">
-        <v>0.053</v>
+        <v>0.4016</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0927</v>
+        <v>0.3974</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5093</v>
+        <v>-0.1061</v>
       </c>
       <c r="F8" t="n">
-        <v>0.602</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.3532</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2049</v>
+        <v>0.0998</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7784</v>
+        <v>-0.3752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5735</v>
+        <v>0.475</v>
       </c>
       <c r="V8" t="n">
         <v>0.315</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0086</v>
+        <v>0.0151</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0504</v>
+        <v>-0.0257</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0418</v>
+        <v>0.0408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7772</v>
+        <v>-0.7066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7173</v>
+        <v>-0.6836</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0599</v>
+        <v>-0.023</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.1288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0644</v>
+        <v>0.1288</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5699</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2827</v>
+        <v>-0.8354</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6529</v>
+        <v>-0.8124</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6299</v>
+        <v>-0.023</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2878</v>
+        <v>0.0917</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4551</v>
+        <v>-0.1545</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1674</v>
+        <v>0.2462</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2853</v>
+        <v>-0.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1783</v>
+        <v>-0.3874</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.107</v>
+        <v>0.2141</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7066</v>
+        <v>0.7772</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6836</v>
+        <v>0.7173</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.023</v>
+        <v>0.0599</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1288</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1288</v>
+        <v>0.0644</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8354</v>
+        <v>1.2827</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8124</v>
+        <v>0.6529</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.023</v>
+        <v>0.6299</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2087</v>
+        <v>0.1231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3071</v>
+        <v>0.1181</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0985</v>
+        <v>0.005</v>
       </c>
       <c r="V10" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0748</v>
+        <v>-1.6285</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3831</v>
+        <v>-0.5675</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6917</v>
+        <v>-1.061</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8543</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8356</v>
+        <v>0.282</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1803</v>
+        <v>-0.3646</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0159</v>
+        <v>0.6466</v>
       </c>
       <c r="V12" t="n">
         <v>0.3144</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2198</v>
+        <v>-1.6892</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9007</v>
+        <v>-0.1661</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.319</v>
+        <v>-1.5231</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.309</v>
+        <v>-0.5569</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.372</v>
+        <v>-0.6813</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9370000000000001</v>
+        <v>0.1244</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9407</v>
+        <v>0.9599</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2878</v>
+        <v>0.8971</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6529</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3683</v>
+        <v>-1.5168</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.5784</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2841</v>
+        <v>0.0616</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0157</v>
+        <v>-0.1884</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0336</v>
+        <v>-0.1996</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0492</v>
+        <v>0.0112</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.2598</v>
+        <v>-1.9932</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4167</v>
+        <v>-1.7481</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8432</v>
+        <v>-0.2452</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5569</v>
+        <v>-1.309</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6813</v>
+        <v>-0.372</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1244</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9599</v>
+        <v>-0.9407</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8971</v>
+        <v>-0.2878</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.6529</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5168</v>
+        <v>-0.3683</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5784</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0616</v>
+        <v>-0.2841</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.759</v>
+        <v>0.2422</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4501</v>
+        <v>0.1191</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3089</v>
+        <v>0.1231</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.0262</v>
+        <v>-3.7992</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.2745</v>
+        <v>-3.2197</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7518</v>
+        <v>-0.5794</v>
       </c>
       <c r="G15" t="n">
         <v>-2.1241</v>
@@ -1624,13 +1624,13 @@
         <v>0.3706</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4198</v>
+        <v>-0.1928</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3619</v>
+        <v>-0.3071</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.058</v>
+        <v>0.1144</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.956900000000001</v>
+        <v>9.7776</v>
       </c>
       <c r="E16" t="n">
-        <v>10.6993</v>
+        <v>11.5199</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.742400000000001</v>
+        <v>-1.7424</v>
       </c>
       <c r="G16" t="n">
         <v>7.3285</v>
@@ -1672,7 +1672,7 @@
         <v>7.558499999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2300000000000005</v>
+        <v>-0.23</v>
       </c>
       <c r="J16" t="n">
         <v>17.3154</v>
@@ -1690,7 +1690,7 @@
         <v>-9.7197</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2671000000000001</v>
+        <v>-0.2671</v>
       </c>
       <c r="P16" t="n">
         <v>-0.9264</v>
@@ -1702,16 +1702,16 @@
         <v>9.264399999999998</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5907</v>
+        <v>0.2299</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.29</v>
+        <v>-3.469199999999999</v>
       </c>
       <c r="U16" t="n">
         <v>3.6993</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1455</v>
+        <v>3.145500000000001</v>
       </c>
       <c r="W16" t="n">
         <v>7.864799999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1302</v>
+        <v>2.8948</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1499</v>
+        <v>3.5623</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0197</v>
+        <v>-0.6675</v>
       </c>
       <c r="G17" t="n">
         <v>0.0235</v>
@@ -1780,13 +1780,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6452</v>
+        <v>0.4098</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3209</v>
+        <v>-0.2667</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3243</v>
+        <v>0.6765</v>
       </c>
       <c r="V17" t="n">
         <v>2.8321</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7043</v>
+        <v>2.5969</v>
       </c>
       <c r="E18" t="n">
-        <v>5.294</v>
+        <v>4.2454</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5898</v>
+        <v>-1.6485</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1869</v>
+        <v>3.513</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5570000000000001</v>
+        <v>-1.3991</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6299</v>
+        <v>4.9121</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6932</v>
+        <v>4.6091</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8637</v>
+        <v>-0.5026</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8294</v>
+        <v>5.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5063</v>
+        <v>-1.0961</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3067</v>
+        <v>-0.8966</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1996</v>
       </c>
       <c r="P18" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1642</v>
+        <v>0.1014</v>
       </c>
       <c r="T18" t="n">
-        <v>0.342</v>
+        <v>-0.3637</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8222</v>
+        <v>0.4651</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9439</v>
+        <v>-1.5733</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2027</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.416</v>
+        <v>2.1488</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4412</v>
+        <v>4.7064</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0253</v>
+        <v>-2.5577</v>
       </c>
       <c r="G19" t="n">
-        <v>3.513</v>
+        <v>1.1869</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3991</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9121</v>
+        <v>0.6299</v>
       </c>
       <c r="J19" t="n">
-        <v>4.6091</v>
+        <v>3.6932</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5026</v>
+        <v>2.8637</v>
       </c>
       <c r="L19" t="n">
-        <v>5.1117</v>
+        <v>0.8294</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0961</v>
+        <v>-2.5063</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8966</v>
+        <v>-2.3067</v>
       </c>
       <c r="O19" t="n">
         <v>-0.1996</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0796</v>
+        <v>0.6087</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1679</v>
+        <v>-0.2456</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0883</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5733</v>
+        <v>-0.9439</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5733</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.798</v>
+        <v>1.9516</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8131</v>
+        <v>1.7103</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0151</v>
+        <v>0.2413</v>
       </c>
       <c r="G20" t="n">
-        <v>0.734</v>
+        <v>1.9379</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1845</v>
+        <v>-0.3615</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9185</v>
+        <v>2.2994</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8863</v>
+        <v>1.9292</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1599</v>
+        <v>0.0215</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7264</v>
+        <v>1.9077</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1522</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.3444</v>
+        <v>-0.383</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1922</v>
+        <v>0.3917</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5081</v>
+        <v>-0.1716</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1467</v>
+        <v>-0.2189</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6548</v>
+        <v>0.0473</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7471</v>
+        <v>1.7888</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7103</v>
+        <v>1.7152</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0368</v>
+        <v>0.0737</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9379</v>
+        <v>0.734</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3615</v>
+        <v>-0.1845</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2994</v>
+        <v>0.9185</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9292</v>
+        <v>2.8863</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0215</v>
+        <v>2.1599</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9077</v>
+        <v>0.7264</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008699999999999999</v>
+        <v>-2.1522</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.383</v>
+        <v>-2.3444</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3917</v>
+        <v>0.1922</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.376</v>
+        <v>0.499</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2189</v>
+        <v>-0.2446</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1572</v>
+        <v>0.7436</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>A. MARQUEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6221</v>
+        <v>0.7228</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6221</v>
+        <v>0.7684</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.0456</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6221</v>
+        <v>-0.2086</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.7063</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6221</v>
+        <v>0.4977</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6221</v>
+        <v>2.1813</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.9834</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6221</v>
+        <v>0.1979</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-2.39</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-2.6897</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.2997</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.6339</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.4865</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.1204</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. MARQUEZ MARQUEZ</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5854</v>
+        <v>0.6221</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6705</v>
+        <v>0.6221</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0851</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2086</v>
+        <v>0.6221</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7063</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4977</v>
+        <v>0.6221</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1813</v>
+        <v>0.6221</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9834</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1979</v>
+        <v>0.6221</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.39</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.6897</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2997</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4964</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5844</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0809</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3315</v>
+        <v>0.0944</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4755</v>
+        <v>0.1817</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.144</v>
+        <v>-0.0872</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1962</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5278</v>
+        <v>0.2907</v>
       </c>
       <c r="T25" t="n">
-        <v>0.434</v>
+        <v>0.1402</v>
       </c>
       <c r="U25" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1505</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0965</v>
+        <v>-1.8439</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5378</v>
+        <v>-1.342</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5587</v>
+        <v>-0.502</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9167</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1798</v>
+        <v>0.0727</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1505</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S. KONE</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.8688</v>
+        <v>-2.4751</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8242</v>
+        <v>-1.8801</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0446</v>
+        <v>-0.595</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.442</v>
+        <v>-3.6838</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9981</v>
+        <v>-0.6946</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4439</v>
+        <v>-2.9892</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-1.6911</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2322</v>
+        <v>0.8374</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5284</v>
+        <v>-2.5285</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6814</v>
+        <v>-1.9927</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.766</v>
+        <v>-1.532</v>
       </c>
       <c r="O27" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.4607</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1674</v>
+        <v>0.097</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.766</v>
+        <v>-0.189</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5986</v>
+        <v>0.286</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>S. KONE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.2928</v>
+        <v>-2.8625</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.2718</v>
+        <v>-1.6283</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.021</v>
+        <v>-1.2341</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.6838</v>
+        <v>-1.442</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6946</v>
+        <v>-0.9981</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.9892</v>
+        <v>-0.4439</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.6911</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8374</v>
+        <v>-0.2322</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.5285</v>
+        <v>-0.5284</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.9927</v>
+        <v>-0.6814</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.532</v>
+        <v>-0.766</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.4607</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.7207</v>
+        <v>-0.161</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5807</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.14</v>
+        <v>0.4091</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>-1.2594</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="29">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.2552</v>
+        <v>-4.529</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.1538</v>
+        <v>-4.6641</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1014</v>
+        <v>0.1351</v>
       </c>
       <c r="G29" t="n">
         <v>-2.3289</v>
@@ -2716,13 +2716,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.7028</v>
+        <v>0.0233</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.0396</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3367</v>
+        <v>0.5733</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-9.4002</v>
+        <v>-8.7302</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.2685</v>
+        <v>-6.8768</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.1317</v>
+        <v>-1.8534</v>
       </c>
       <c r="G30" t="n">
         <v>-6.1918</v>
@@ -2794,13 +2794,13 @@
         <v>1.6676</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.5245</v>
+        <v>0.1455</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.0184</v>
+        <v>-0.6267</v>
       </c>
       <c r="U30" t="n">
-        <v>0.4939</v>
+        <v>0.7722</v>
       </c>
       <c r="V30" t="n">
         <v>-1.5722</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-8.956799999999998</v>
+        <v>-6.998399999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.742599999999999</v>
+        <v>1.742600000000002</v>
       </c>
       <c r="F31" t="n">
-        <v>-10.6996</v>
+        <v>-8.7409</v>
       </c>
       <c r="G31" t="n">
         <v>-7.3285</v>
@@ -2842,16 +2842,16 @@
         <v>-7.5585</v>
       </c>
       <c r="I31" t="n">
-        <v>0.23</v>
+        <v>0.2299999999999991</v>
       </c>
       <c r="J31" t="n">
         <v>9.986999999999998</v>
       </c>
       <c r="K31" t="n">
-        <v>9.719700000000001</v>
+        <v>9.7197</v>
       </c>
       <c r="L31" t="n">
-        <v>0.267199999999999</v>
+        <v>0.2671999999999963</v>
       </c>
       <c r="M31" t="n">
         <v>-17.3154</v>
@@ -2860,7 +2860,7 @@
         <v>-17.2784</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.03709999999999991</v>
+        <v>-0.03710000000000002</v>
       </c>
       <c r="P31" t="n">
         <v>0.9264999999999999</v>
@@ -2872,13 +2872,13 @@
         <v>10.1909</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5909000000000002</v>
+        <v>2.5494</v>
       </c>
       <c r="T31" t="n">
-        <v>-3.6993</v>
+        <v>-3.6992</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2901</v>
+        <v>6.248799999999999</v>
       </c>
       <c r="V31" t="n">
         <v>-3.1456</v>
